--- a/artfynd/A 54128-2023 artfynd.xlsx
+++ b/artfynd/A 54128-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658632</v>
+        <v>117658689</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418174</v>
+        <v>418073</v>
       </c>
       <c r="R2" t="n">
-        <v>7045772</v>
+        <v>7045708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658689</v>
+        <v>117658632</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418073</v>
+        <v>418174</v>
       </c>
       <c r="R3" t="n">
-        <v>7045708</v>
+        <v>7045772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54128-2023 artfynd.xlsx
+++ b/artfynd/A 54128-2023 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>117658689</v>
       </c>
       <c r="B2" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -785,12 +780,7 @@
         <v>117658632</v>
       </c>
       <c r="B3" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54128-2023 artfynd.xlsx
+++ b/artfynd/A 54128-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117658689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117658632</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>